--- a/InputData/indst/_cement/BCPCS/BAU Cement Pathway Capital Subsidy.xlsx
+++ b/InputData/indst/_cement/BCPCS/BAU Cement Pathway Capital Subsidy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanOBrien\Models\EPS\US\eps-us\InputData\indst\_cement\BCPCS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD9C0CE2-26A0-412A-8380-718728DA9176}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23FFF9A3-4EFF-43A4-A462-4565B4000446}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31095" yWindow="2295" windowWidth="21600" windowHeight="12585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="12525" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
   <si>
     <t>BCPCS BAU Cement Pathway Capital Subsidy</t>
   </si>
@@ -138,13 +138,22 @@
   </si>
   <si>
     <t>Unit: dimensionless</t>
+  </si>
+  <si>
+    <t>electric kiln with CCS</t>
+  </si>
+  <si>
+    <t>Electric kiln with CCS</t>
+  </si>
+  <si>
+    <t>The electric kiln with CCS is the electric kiln with a capture unit on its nearly pure CO2 stream, so it uses the electric kiln's value here (same kiln). Its capture is added through CCF (95 percent of calcination CO2 captured) and the CDSC capture inputs.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -168,6 +177,14 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -202,7 +219,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -224,6 +241,12 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -526,7 +549,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -636,6 +659,14 @@
       </c>
       <c r="B22" s="3" t="s">
         <v>20</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+      <c r="A23" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="B23" s="9" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -1202,7 +1233,7 @@
   <sheetPr>
     <tabColor rgb="FF1F3864"/>
   </sheetPr>
-  <dimension ref="A1:AE5"/>
+  <dimension ref="A1:AE6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -1682,127 +1713,252 @@
       </c>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A5" t="str">
+      <c r="A5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B5">
+        <f>B4</f>
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <f>C4</f>
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <f>D4</f>
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <f>E4</f>
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <f>F4</f>
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <f>G4</f>
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <f>H4</f>
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <f>I4</f>
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <f>J4</f>
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <f>K4</f>
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <f>L4</f>
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <f>M4</f>
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <f>N4</f>
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <f>O4</f>
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <f>P4</f>
+        <v>0</v>
+      </c>
+      <c r="Q5">
+        <f>Q4</f>
+        <v>0</v>
+      </c>
+      <c r="R5">
+        <f>R4</f>
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <f>S4</f>
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <f>T4</f>
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <f>U4</f>
+        <v>0</v>
+      </c>
+      <c r="V5">
+        <f>V4</f>
+        <v>0</v>
+      </c>
+      <c r="W5">
+        <f>W4</f>
+        <v>0</v>
+      </c>
+      <c r="X5">
+        <f>X4</f>
+        <v>0</v>
+      </c>
+      <c r="Y5">
+        <f>Y4</f>
+        <v>0</v>
+      </c>
+      <c r="Z5">
+        <f>Z4</f>
+        <v>0</v>
+      </c>
+      <c r="AA5">
+        <f>AA4</f>
+        <v>0</v>
+      </c>
+      <c r="AB5">
+        <f>AB4</f>
+        <v>0</v>
+      </c>
+      <c r="AC5">
+        <f>AC4</f>
+        <v>0</v>
+      </c>
+      <c r="AD5">
+        <f>AD4</f>
+        <v>0</v>
+      </c>
+      <c r="AE5">
+        <f>AE4</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A6" t="str">
         <f>'Subsidy Rates'!A7</f>
         <v>alternative chemistry cement</v>
       </c>
-      <c r="B5">
+      <c r="B6">
         <f>'Subsidy Rates'!B7</f>
         <v>0</v>
       </c>
-      <c r="C5">
+      <c r="C6">
         <f>'Subsidy Rates'!C7</f>
         <v>0</v>
       </c>
-      <c r="D5">
+      <c r="D6">
         <f>'Subsidy Rates'!D7</f>
         <v>0</v>
       </c>
-      <c r="E5">
+      <c r="E6">
         <f>'Subsidy Rates'!E7</f>
         <v>0</v>
       </c>
-      <c r="F5">
+      <c r="F6">
         <f>'Subsidy Rates'!F7</f>
         <v>0</v>
       </c>
-      <c r="G5">
+      <c r="G6">
         <f>'Subsidy Rates'!G7</f>
         <v>0</v>
       </c>
-      <c r="H5">
+      <c r="H6">
         <f>'Subsidy Rates'!H7</f>
         <v>0</v>
       </c>
-      <c r="I5">
+      <c r="I6">
         <f>'Subsidy Rates'!I7</f>
         <v>0</v>
       </c>
-      <c r="J5">
+      <c r="J6">
         <f>'Subsidy Rates'!J7</f>
         <v>0</v>
       </c>
-      <c r="K5">
+      <c r="K6">
         <f>'Subsidy Rates'!K7</f>
         <v>0</v>
       </c>
-      <c r="L5">
+      <c r="L6">
         <f>'Subsidy Rates'!L7</f>
         <v>0</v>
       </c>
-      <c r="M5">
+      <c r="M6">
         <f>'Subsidy Rates'!M7</f>
         <v>0</v>
       </c>
-      <c r="N5">
+      <c r="N6">
         <f>'Subsidy Rates'!N7</f>
         <v>0</v>
       </c>
-      <c r="O5">
+      <c r="O6">
         <f>'Subsidy Rates'!O7</f>
         <v>0</v>
       </c>
-      <c r="P5">
+      <c r="P6">
         <f>'Subsidy Rates'!P7</f>
         <v>0</v>
       </c>
-      <c r="Q5">
+      <c r="Q6">
         <f>'Subsidy Rates'!Q7</f>
         <v>0</v>
       </c>
-      <c r="R5">
+      <c r="R6">
         <f>'Subsidy Rates'!R7</f>
         <v>0</v>
       </c>
-      <c r="S5">
+      <c r="S6">
         <f>'Subsidy Rates'!S7</f>
         <v>0</v>
       </c>
-      <c r="T5">
+      <c r="T6">
         <f>'Subsidy Rates'!T7</f>
         <v>0</v>
       </c>
-      <c r="U5">
+      <c r="U6">
         <f>'Subsidy Rates'!U7</f>
         <v>0</v>
       </c>
-      <c r="V5">
+      <c r="V6">
         <f>'Subsidy Rates'!V7</f>
         <v>0</v>
       </c>
-      <c r="W5">
+      <c r="W6">
         <f>'Subsidy Rates'!W7</f>
         <v>0</v>
       </c>
-      <c r="X5">
+      <c r="X6">
         <f>'Subsidy Rates'!X7</f>
         <v>0</v>
       </c>
-      <c r="Y5">
+      <c r="Y6">
         <f>'Subsidy Rates'!Y7</f>
         <v>0</v>
       </c>
-      <c r="Z5">
+      <c r="Z6">
         <f>'Subsidy Rates'!Z7</f>
         <v>0</v>
       </c>
-      <c r="AA5">
+      <c r="AA6">
         <f>'Subsidy Rates'!AA7</f>
         <v>0</v>
       </c>
-      <c r="AB5">
+      <c r="AB6">
         <f>'Subsidy Rates'!AB7</f>
         <v>0</v>
       </c>
-      <c r="AC5">
+      <c r="AC6">
         <f>'Subsidy Rates'!AC7</f>
         <v>0</v>
       </c>
-      <c r="AD5">
+      <c r="AD6">
         <f>'Subsidy Rates'!AD7</f>
         <v>0</v>
       </c>
-      <c r="AE5">
+      <c r="AE6">
         <f>'Subsidy Rates'!AE7</f>
         <v>0</v>
       </c>
